--- a/product_upload/packages/37/file.xlsx
+++ b/product_upload/packages/37/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -836,6 +841,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>JAKAVI 5MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-DB8BAB31D0D7</t>
         </is>
       </c>
@@ -859,7 +869,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1026,6 +1036,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>RESTASIS 0.05% Eye Drop Emulsion</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-F2175CE4BAF2</t>
         </is>
       </c>
@@ -1049,7 +1064,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1220,6 +1235,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>COSOPT EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-99399FF2819A</t>
         </is>
       </c>
@@ -1243,7 +1263,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1414,6 +1434,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>ROLENIUM 250/50 mcg Elpenhaler</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-12556242DF4D</t>
         </is>
       </c>
@@ -1437,7 +1462,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1600,6 +1625,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>JAKAVI 15MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-520172C99AB7</t>
         </is>
       </c>
@@ -1623,7 +1653,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1794,6 +1824,11 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>LODIPAM 10 mg Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-9E09147FD1C2</t>
         </is>
       </c>
@@ -1817,7 +1852,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1988,6 +2023,11 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>CITOXAL 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-F109B7054F0F</t>
         </is>
       </c>
@@ -2011,7 +2051,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2182,6 +2222,11 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>CITOXAL 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-E70FF504ACB0</t>
         </is>
       </c>
@@ -2205,7 +2250,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2364,6 +2409,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>LODIPAM 2.5 mg Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-DDE208B669EE</t>
         </is>
       </c>
@@ -2387,7 +2437,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2546,6 +2596,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>FLOMOCIN 400 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-D2348A0C3AF7</t>
         </is>
       </c>
@@ -2569,7 +2624,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2724,6 +2779,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>FLOMOCIN 400 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-6551DBE1F986</t>
         </is>
       </c>
@@ -2747,7 +2807,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2914,6 +2974,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>ZOLIX 0.5 mg/ml Oral Solution</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-EA4224FB17D1</t>
         </is>
       </c>
@@ -2937,7 +3002,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3100,6 +3165,11 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>BUTAFYL 1% W/V SPRAY</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-156BD00B44A3</t>
         </is>
       </c>
@@ -3123,7 +3193,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3286,6 +3356,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>DEXTROSE 5% + 0.45% SODIUM CHLORIDE INJECTION</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-1AA768051FD9</t>
         </is>
       </c>
@@ -3309,7 +3384,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3472,6 +3547,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>5 % w/v DEXTROSE Injection 500 ml</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-33A12F942E34</t>
         </is>
       </c>
@@ -3495,7 +3575,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3654,6 +3734,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>EREVARD 10MG Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-29B0035237FF</t>
         </is>
       </c>
@@ -3677,7 +3762,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3844,6 +3929,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>EREVARD 20MG Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-E91FA2028CEE</t>
         </is>
       </c>
@@ -3867,7 +3957,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4034,6 +4124,11 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>DEXTROSE 5% + 0.9% SODIUM CHLORIDE INJECTION</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-5005CBE3A8AA</t>
         </is>
       </c>
@@ -4057,7 +4152,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4224,6 +4319,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>IRBEGEN PLUS 150/12.5 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-472D3D2B76C4</t>
         </is>
       </c>
@@ -4247,7 +4347,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4414,6 +4514,11 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>IRBEGEN PLUS 300/25 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-3F9BD74A89A9</t>
         </is>
       </c>
@@ -4437,7 +4542,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4602,6 +4707,11 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>CINAC 30 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-872C62C9EF7D</t>
         </is>
       </c>
@@ -4625,7 +4735,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4786,6 +4896,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>CINAC 60 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-A5F4145C3A8D</t>
         </is>
       </c>
@@ -4809,7 +4924,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4976,6 +5091,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>HEROX 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-BAD61FAA5DE2</t>
         </is>
       </c>
@@ -4999,7 +5119,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5158,6 +5278,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>LEUKAST 4 mg Granules</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-004F0ED5183B</t>
         </is>
       </c>
@@ -5181,7 +5306,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5344,6 +5469,11 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>QUTENZA 179 mg Cutaneous Patch</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-B3E177034F04</t>
         </is>
       </c>
@@ -5367,7 +5497,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5522,6 +5652,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>QUTENZA 179 mg Cutaneous Patch</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-C3E9842FF907</t>
         </is>
       </c>
@@ -5545,7 +5680,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5708,6 +5843,11 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>LEVETAM 100 mg/ml Oral Solution</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-4B431C266B4F</t>
         </is>
       </c>
@@ -5731,7 +5871,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5898,6 +6038,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>HYFRESH EYE GEL UD</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-62E21DA534A2</t>
         </is>
       </c>
@@ -5921,7 +6066,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6088,6 +6233,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>TEDO 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-082D4852357B</t>
         </is>
       </c>
@@ -6111,7 +6261,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6266,6 +6416,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>ALLERTEC 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-04B7D9EA3039</t>
         </is>
       </c>
@@ -6289,7 +6444,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6452,6 +6607,11 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>FEGONA 0.5 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-7E72D142A249</t>
         </is>
       </c>
@@ -6475,7 +6635,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6638,6 +6798,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>EVOX 750MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-FE7ACA351AD4</t>
         </is>
       </c>
@@ -6661,7 +6826,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6820,6 +6985,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>EVOX 500MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-BED0E8C53525</t>
         </is>
       </c>
@@ -6843,7 +7013,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7006,6 +7176,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>EVOX 250MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-1886C98404B2</t>
         </is>
       </c>
@@ -7029,7 +7204,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7196,6 +7371,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>ARTIZ 10 MG F.C TABLET</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-5B314BBC160D</t>
         </is>
       </c>
@@ -7219,7 +7399,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7388,6 +7568,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>RIFINAH</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-3AA2A98E0AC4</t>
         </is>
       </c>
@@ -7411,7 +7596,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7580,6 +7765,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>RIFINAH</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-817ED00891A7</t>
         </is>
       </c>
@@ -7603,7 +7793,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7766,6 +7956,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>TRAVATAN EYE DROP</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-737F1E512302</t>
         </is>
       </c>
@@ -7789,7 +7984,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7964,6 +8159,11 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>MIRVASO 3 MG/G GEL</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-42AEAAE94C95</t>
         </is>
       </c>
@@ -7987,7 +8187,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8158,6 +8358,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>ESCITAM 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-B733C5619878</t>
         </is>
       </c>
@@ -8181,7 +8386,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8352,6 +8557,11 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>NIZORTAN 40 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-47EC2F96659D</t>
         </is>
       </c>
@@ -8375,7 +8585,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8542,6 +8752,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>NIZORTAN 80 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-AF0390DC2166</t>
         </is>
       </c>
@@ -8565,7 +8780,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8732,6 +8947,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>ESCITAM 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-DEFC2212E9E2</t>
         </is>
       </c>
@@ -8755,7 +8975,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8926,6 +9146,11 @@
       </c>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>FUSIDERM 2% CREAM</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-E74CBEDE5E35</t>
         </is>
       </c>
@@ -8949,7 +9174,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9116,6 +9341,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>SOLFISAN 5 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-66209CE08A18</t>
         </is>
       </c>
@@ -9139,7 +9369,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9306,6 +9536,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>SOLFISAN 10 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-F16AC30D18AA</t>
         </is>
       </c>
@@ -9329,7 +9564,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9504,6 +9739,11 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>EPCLUSA 400 mg/100 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-6FEC62EB8CE5</t>
         </is>
       </c>
@@ -9527,7 +9767,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9686,6 +9926,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>ALLAIR 10 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-099E05B811F5</t>
         </is>
       </c>
@@ -9709,7 +9954,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9868,6 +10113,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>RIALOCAINE 2 % Gel</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-A8331C778A75</t>
         </is>
       </c>
@@ -9891,7 +10141,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10054,6 +10304,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>MOXICLAV 1 gm Film Coted Tablet</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-08B38438CE1B</t>
         </is>
       </c>
@@ -10077,7 +10332,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10248,6 +10503,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>TRAMAL RETARD 100MG F.C TAB</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-6C9E2CED9EAF</t>
         </is>
       </c>
@@ -10271,7 +10531,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10446,6 +10706,11 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>VENTAVIS 10 mcg/ml solution for inhalation</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-6AC740207962</t>
         </is>
       </c>
@@ -10469,7 +10734,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10638,6 +10903,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>POSTINOR-2</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-24EC0D6EBE89</t>
         </is>
       </c>
@@ -10661,7 +10931,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10840,6 +11110,11 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>CARDEX</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-22BD170EF954</t>
         </is>
       </c>
@@ -10863,7 +11138,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11030,6 +11305,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>CARDEX 10 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-2066F006B298</t>
         </is>
       </c>
@@ -11053,7 +11333,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11220,6 +11500,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>CARDEX PLUS 10/25 mg F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-8B48AAC4418F</t>
         </is>
       </c>
@@ -11243,7 +11528,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11410,6 +11695,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>CARDEX PLUS 5/12.5 mg F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-15DAFCD02C1A</t>
         </is>
       </c>
@@ -11433,7 +11723,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11600,6 +11890,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>TOBRADEX EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-9CDB54CB80C1</t>
         </is>
       </c>
@@ -11623,7 +11918,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11790,6 +12085,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>MAXITROL</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-053BE7349192</t>
         </is>
       </c>
@@ -11813,7 +12113,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11968,6 +12268,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>ARPEK 250 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-BBD68244AFDB</t>
         </is>
       </c>
@@ -11991,7 +12296,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12150,6 +12455,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>ARPEK 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-4A7AB72335DB</t>
         </is>
       </c>
@@ -12173,7 +12483,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12344,6 +12654,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>SALAZOPYRIN-EN TAB 500MG</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-5B089ED622E4</t>
         </is>
       </c>
@@ -12367,7 +12682,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12546,6 +12861,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>CARDEX 5 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-EA62ECADC199</t>
         </is>
       </c>
@@ -12569,7 +12889,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12744,6 +13064,11 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>VOLCON 200 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-FDCCF97A143F</t>
         </is>
       </c>
@@ -12767,7 +13092,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12930,6 +13255,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>ENTAVIR 0.5 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-1DFEC51FFEFC</t>
         </is>
       </c>
@@ -12953,7 +13283,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13112,6 +13442,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>ENTAVIR 1 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-8DD63C17DF46</t>
         </is>
       </c>
@@ -13135,7 +13470,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13298,6 +13633,11 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>LOVERA 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-EF26CC413649</t>
         </is>
       </c>
@@ -13321,7 +13661,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13484,6 +13824,11 @@
       </c>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>LOVERA 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-B4756B927509</t>
         </is>
       </c>
@@ -13507,7 +13852,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13670,6 +14015,11 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>LOVERA 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-567FA0C2868D</t>
         </is>
       </c>
@@ -13693,7 +14043,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13864,6 +14214,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>GANFORT EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-45BADD8F170B</t>
         </is>
       </c>
@@ -13887,7 +14242,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14046,6 +14401,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>AMLOBEN 5 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-0D77E9D21ED4</t>
         </is>
       </c>
@@ -14069,7 +14429,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14226,6 +14586,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>REXULTI 0.25 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-75104112BD3A</t>
         </is>
       </c>
@@ -14249,7 +14614,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14414,6 +14779,11 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>REXULTI 0.5 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-9E371444F042</t>
         </is>
       </c>
@@ -14437,7 +14807,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14606,6 +14976,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>REXULTI 2 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-F7C7ADB7271C</t>
         </is>
       </c>
@@ -14629,7 +15004,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14798,6 +15173,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>REXULTI 3 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-61C484372AFB</t>
         </is>
       </c>
@@ -14821,7 +15201,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14986,6 +15366,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>REXULTI 4 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-95407EF6A1BF</t>
         </is>
       </c>
@@ -15009,7 +15394,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15176,6 +15561,11 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>GLOZAL 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-3334E51B8291</t>
         </is>
       </c>
@@ -15199,7 +15589,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15366,6 +15756,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>GLOZAL 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-BDCDE4598A4C</t>
         </is>
       </c>
@@ -15389,7 +15784,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15568,6 +15963,11 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>RIVETAL 1.5 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-622758CEAEA9</t>
         </is>
       </c>
@@ -15591,7 +15991,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15770,6 +16170,11 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>RIVETAL 3 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-D52458EDD632</t>
         </is>
       </c>
@@ -15793,7 +16198,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15968,6 +16373,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>RIVETAL 4.5 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-3763F699649E</t>
         </is>
       </c>
@@ -15991,7 +16401,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16162,6 +16572,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>RIVETAL 6 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-7A08056EAA19</t>
         </is>
       </c>
@@ -16185,7 +16600,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16354,6 +16769,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>REXULTI 1 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-95CF55041CF9</t>
         </is>
       </c>
@@ -16377,7 +16797,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16536,6 +16956,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>MIXIF 400 mg Capsules</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-4ED0395C9F67</t>
         </is>
       </c>
@@ -16559,7 +16984,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16730,6 +17155,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>SYNJARDY 5/850 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-5362B2C7E5D3</t>
         </is>
       </c>
@@ -16753,7 +17183,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16920,6 +17350,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>SYNJARDY 5/1000 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-1B579BE9F9DE</t>
         </is>
       </c>
@@ -16943,7 +17378,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17114,6 +17549,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>SYNJARDY 12.5/850 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-FB7E6B2F83F9</t>
         </is>
       </c>
@@ -17137,7 +17577,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17304,6 +17744,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>SYNJARDY 12.5/1000 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-256EC5A7625B</t>
         </is>
       </c>
@@ -17327,7 +17772,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17492,6 +17937,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>MYORA 500 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-1C6E34366EE6</t>
         </is>
       </c>
@@ -17515,7 +17965,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17678,6 +18128,11 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>ANNUVA 50 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-42FB0F2279D5</t>
         </is>
       </c>
@@ -17701,7 +18156,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17860,6 +18315,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>SERCAND 25 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-8D38D317FEC7</t>
         </is>
       </c>
@@ -17883,7 +18343,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18054,6 +18514,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>DESLORATADINE/GENEPHARM 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-7AFBA78DF693</t>
         </is>
       </c>
@@ -18077,7 +18542,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18248,6 +18713,11 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>MONCAS 5 mg Chewable Tablet</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-79B0AADC0C49</t>
         </is>
       </c>
@@ -18271,7 +18741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18442,6 +18912,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>SPIOLTO RESPIMATE</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-AD5BA16B1F05</t>
         </is>
       </c>
@@ -18465,7 +18940,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18628,6 +19103,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>SPEDRA 50 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-8D1B96759218</t>
         </is>
       </c>
@@ -18651,7 +19131,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18818,6 +19298,11 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>PANLOCK 40 mg Enteric coated tablet</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-FD5E389CE4FF</t>
         </is>
       </c>
@@ -18841,7 +19326,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -19004,6 +19489,11 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>SPEDRA 100 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-F8E1BC52AB9B</t>
         </is>
       </c>
@@ -19027,7 +19517,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19200,6 +19690,11 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>LINDYNETTE 0.075/0.03 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-E579DDBC953A</t>
         </is>
       </c>
@@ -19223,7 +19718,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19386,6 +19881,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>GENVOYA Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-0729F17FC9E9</t>
         </is>
       </c>
@@ -19409,7 +19909,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19579,6 +20079,11 @@
         </is>
       </c>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>ROZLET 2.5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-C95016F8C240</t>
         </is>
@@ -19595,7 +20100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19641,100 +20146,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19766,7 +20276,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19781,92 +20291,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-45382</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>149.22</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>319</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19898,7 +20413,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19913,92 +20428,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-87174</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>430.37</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>320</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20030,7 +20550,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20045,92 +20565,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-34906</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>12.79</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>321</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20162,7 +20687,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20177,92 +20702,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-61071</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>440.35</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>322</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20294,7 +20824,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20309,92 +20839,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-90435</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>135.21</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>323</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20426,7 +20961,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20441,92 +20976,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-38446</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>149.76</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>324</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20558,7 +21098,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20573,92 +21113,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-61152</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>49.78</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>325</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20690,7 +21235,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20705,92 +21250,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-54837</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>425.11</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>326</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20822,7 +21372,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20837,92 +21387,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-29425</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>271.68</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>327</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20954,7 +21509,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20969,92 +21524,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-25480</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>219.73</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>328</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21086,7 +21646,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21101,92 +21661,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-97678</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>17.54</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>329</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21203,7 +21768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21309,6 +21874,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21344,7 +21919,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21409,6 +21984,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-4F1BB2D7CC95</t>
         </is>
@@ -21445,7 +22030,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21510,6 +22095,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-522165D91703</t>
         </is>
@@ -21546,7 +22141,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21611,6 +22206,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-8961E16D30C1</t>
         </is>
@@ -21647,7 +22252,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21712,6 +22317,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-174A946497E9</t>
         </is>
@@ -21748,7 +22363,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21813,6 +22428,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-4DC8A468E7B3</t>
         </is>
@@ -21849,7 +22474,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21914,6 +22539,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-EC6AABD9421D</t>
         </is>
@@ -21950,7 +22585,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22015,6 +22650,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-ABA3D6476397</t>
         </is>
@@ -22051,7 +22696,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22116,6 +22761,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-EC2F214006D2</t>
         </is>
@@ -22152,7 +22807,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22217,6 +22872,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-EF1EE8B45B53</t>
         </is>
@@ -22253,7 +22918,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22318,6 +22983,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-35D75A9D1B1A</t>
         </is>
@@ -22354,7 +23029,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22419,6 +23094,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-77802E3CE17A</t>
         </is>
@@ -22455,7 +23140,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22520,6 +23205,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-FC8F03143755</t>
         </is>
@@ -22556,7 +23251,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22621,6 +23316,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-F6D7F80C3B45</t>
         </is>
@@ -22657,7 +23362,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22722,6 +23427,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-685F5FF9E1D1</t>
         </is>
@@ -22758,7 +23473,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22823,6 +23538,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-7CA36C7793FC</t>
         </is>
@@ -22859,7 +23584,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22924,6 +23649,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-502E4C2E62EC</t>
         </is>
@@ -22960,7 +23695,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23025,6 +23760,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-2CC36EFDF021</t>
         </is>
@@ -23061,7 +23806,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23126,6 +23871,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-C28105DED44C</t>
         </is>
@@ -23162,7 +23917,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23227,6 +23982,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-AC1FC1B2F57B</t>
         </is>
@@ -23263,7 +24028,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23328,6 +24093,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-86C445ED094F</t>
         </is>

--- a/product_upload/packages/37/file.xlsx
+++ b/product_upload/packages/37/file.xlsx
@@ -2258,8 +2258,16 @@
           <t>7941157533-843-932584241573</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LODIPAM 2.5 mg Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>LODIPAM 2.5 mg Film-Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2445,8 +2453,16 @@
           <t>6790142664-617-749504405363</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLOMOCIN 400 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>FLOMOCIN 400 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2632,8 +2648,16 @@
           <t>4366273826-496-451772782489</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLOMOCIN 400 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>FLOMOCIN 400 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -3010,8 +3034,16 @@
           <t>8704927400-288-952102715259</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BUTAFYL 1% W/V SPRAY</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>BUTAFYL 1% W/V SPRAY detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3201,8 +3233,16 @@
           <t>2658950422-652-898315059840</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5% + 0.45% SODIUM CHLORIDE INJECTION</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% + 0.45% SODIUM CHLORIDE INJECTION detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3392,8 +3432,16 @@
           <t>7465325103-803-546402025769</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 5 % w/v DEXTROSE Injection 500 ml</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>5 % w/v DEXTROSE Injection 500 ml detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3583,8 +3631,16 @@
           <t>8276354705-588-055441840905</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EREVARD 10MG Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>EREVARD 10MG Film-Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3965,8 +4021,16 @@
           <t>4689435880-538-111879814929</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5% + 0.9% SODIUM CHLORIDE INJECTION</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5% + 0.9% SODIUM CHLORIDE INJECTION detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4160,8 +4224,16 @@
           <t>6729143708-431-612803597796</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IRBEGEN PLUS 150/12.5 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>IRBEGEN PLUS 150/12.5 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4355,8 +4427,16 @@
           <t>1834114909-020-029610771624</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IRBEGEN PLUS 300/25 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>IRBEGEN PLUS 300/25 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4550,8 +4630,16 @@
           <t>7351159192-368-987037742843</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CINAC 30 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>CINAC 30 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>AJA PHARMACEUTICAL INDUSTRIES</t>
@@ -4743,8 +4831,16 @@
           <t>0949098520-418-592781331512</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CINAC 60 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>CINAC 60 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>AJA PHARMACEUTICAL INDUSTRIES</t>
@@ -5127,8 +5223,16 @@
           <t>0613555966-320-173837957213</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEUKAST 4 mg Granules</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>LEUKAST 4 mg Granules detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5314,8 +5418,16 @@
           <t>3838643485-576-255384355767</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUTENZA 179 mg Cutaneous Patch</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>QUTENZA 179 mg Cutaneous Patch detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5505,8 +5617,16 @@
           <t>8265346924-998-993228669676</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUTENZA 179 mg Cutaneous Patch</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>QUTENZA 179 mg Cutaneous Patch detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5688,8 +5808,16 @@
           <t>6445817120-473-606074524918</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEVETAM 100 mg/ml Oral Solution</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>LEVETAM 100 mg/ml Oral Solution detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -6269,8 +6397,16 @@
           <t>1654378112-502-837116480684</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALLERTEC 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ALLERTEC 5 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6452,8 +6588,16 @@
           <t>0136502269-517-226155770431</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FEGONA 0.5 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>FEGONA 0.5 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6643,8 +6787,16 @@
           <t>3499113940-960-700642129817</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EVOX 750MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>EVOX 750MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6834,8 +6986,16 @@
           <t>0569477907-173-060941950610</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EVOX 500MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>EVOX 500MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -7021,8 +7181,16 @@
           <t>5198367092-263-838113129036</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EVOX 250MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>EVOX 250MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -9775,8 +9943,16 @@
           <t>7578933500-305-480475596962</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALLAIR 10 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>ALLAIR 10 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -9962,8 +10138,16 @@
           <t>2270211128-517-955079105174</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RIALOCAINE 2 % Gel</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>RIALOCAINE 2 % Gel detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -10149,8 +10333,16 @@
           <t>5855805475-368-367153844850</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MOXICLAV 1 gm Film Coted Tablet</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>MOXICLAV 1 gm Film Coted Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -11146,8 +11338,16 @@
           <t>1012415876-548-660973874121</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CARDEX 10 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>CARDEX 10 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -11341,8 +11541,16 @@
           <t>2703054440-437-176553415834</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CARDEX PLUS 10/25 mg F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>CARDEX PLUS 10/25 mg F.C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11536,8 +11744,16 @@
           <t>2130450831-832-799184162498</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CARDEX PLUS 5/12.5 mg F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>CARDEX PLUS 5/12.5 mg F.C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -12121,8 +12337,16 @@
           <t>8588115663-187-147626565938</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARPEK 250 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>ARPEK 250 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12304,8 +12528,16 @@
           <t>4212939978-120-935065227980</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARPEK 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>ARPEK 500 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -13100,8 +13332,16 @@
           <t>2418433179-172-699090877741</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ENTAVIR 0.5 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>ENTAVIR 0.5 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -13291,8 +13531,16 @@
           <t>1230574885-501-877794793382</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ENTAVIR 1 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>ENTAVIR 1 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13478,8 +13726,16 @@
           <t>8817254243-858-139012517578</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOVERA 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>LOVERA 5 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13669,8 +13925,16 @@
           <t>7881031673-088-631467199598</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOVERA 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>LOVERA 20 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13860,8 +14124,16 @@
           <t>8130571745-819-561673562429</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOVERA 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>LOVERA 20 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -14250,8 +14522,16 @@
           <t>7618631591-756-800276864625</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMLOBEN 5 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>AMLOBEN 5 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -14437,8 +14717,16 @@
           <t>6481242938-598-811255536062</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REXULTI 0.25 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>REXULTI 0.25 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
           <t>AJA PHARMACEUTICAL INDUSTRIES</t>
@@ -14622,8 +14910,16 @@
           <t>8554610059-433-549568891854</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REXULTI 0.5 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>REXULTI 0.5 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
           <t>AJA PHARMACEUTICAL INDUSTRIES</t>
@@ -15402,8 +15698,16 @@
           <t>1855064158-552-309928837543</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLOZAL 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>GLOZAL 5 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -16805,8 +17109,16 @@
           <t>5323778379-323-643744513575</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MIXIF 400 mg Capsules</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>MIXIF 400 mg Capsules detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -17780,8 +18092,16 @@
           <t>2060396402-036-309320374264</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MYORA 500 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>MYORA 500 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
           <t>Jazeera Pharmaceutical Industries (JPI)</t>
@@ -17973,8 +18293,16 @@
           <t>0308880461-535-543847441876</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ANNUVA 50 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>ANNUVA 50 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -18164,8 +18492,16 @@
           <t>6319436561-984-224582928988</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SERCAND 25 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>SERCAND 25 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -18351,8 +18687,16 @@
           <t>8189985889-289-266691749961</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DESLORATADINE/GENEPHARM 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>DESLORATADINE/GENEPHARM 5 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -18550,8 +18894,16 @@
           <t>3026530277-503-558139971884</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MONCAS 5 mg Chewable Tablet</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>MONCAS 5 mg Chewable Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18948,8 +19300,16 @@
           <t>8631723705-888-667038545421</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SPEDRA 50 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>SPEDRA 50 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -19139,8 +19499,16 @@
           <t>1625383978-028-138248997613</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PANLOCK 40 mg Enteric coated tablet</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>PANLOCK 40 mg Enteric coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -19334,8 +19702,16 @@
           <t>6832047071-267-447288141982</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SPEDRA 100 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>SPEDRA 100 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -19726,8 +20102,16 @@
           <t>0068698700-053-335869666773</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GENVOYA Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>GENVOYA Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/37/file.xlsx
+++ b/product_upload/packages/37/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20530,7 +20530,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22152,7 +22152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22233,40 +22233,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22346,38 +22351,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>14.89</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-4F1BB2D7CC95</t>
         </is>
@@ -22457,38 +22467,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>390.61</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-522165D91703</t>
         </is>
@@ -22568,38 +22583,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>143.39</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-8961E16D30C1</t>
         </is>
@@ -22679,38 +22699,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>77.41</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-174A946497E9</t>
         </is>
@@ -22790,38 +22815,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>103.81</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-4DC8A468E7B3</t>
         </is>
@@ -22901,38 +22931,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>368.04</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-EC6AABD9421D</t>
         </is>
@@ -23012,38 +23047,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>275.79</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-ABA3D6476397</t>
         </is>
@@ -23123,38 +23163,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>385.18</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-EC2F214006D2</t>
         </is>
@@ -23234,38 +23279,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>80.69</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-EF1EE8B45B53</t>
         </is>
@@ -23345,38 +23395,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>114.5</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-35D75A9D1B1A</t>
         </is>
@@ -23456,38 +23511,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>277.55</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-77802E3CE17A</t>
         </is>
@@ -23567,38 +23627,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>119.39</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-FC8F03143755</t>
         </is>
@@ -23678,38 +23743,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>234.23</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-F6D7F80C3B45</t>
         </is>
@@ -23789,38 +23859,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>116.63</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-685F5FF9E1D1</t>
         </is>
@@ -23900,38 +23975,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>233.04</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-7CA36C7793FC</t>
         </is>
@@ -24011,38 +24091,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>48.96</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-502E4C2E62EC</t>
         </is>
@@ -24122,38 +24207,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>225.09</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-2CC36EFDF021</t>
         </is>
@@ -24233,38 +24323,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>255.11</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-C28105DED44C</t>
         </is>
@@ -24344,38 +24439,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>185.7</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-AC1FC1B2F57B</t>
         </is>
@@ -24455,38 +24555,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>494.09</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-86C445ED094F</t>
         </is>
